--- a/public/plantillas/8. ESTUDIO DEL MERCADO.xlsx
+++ b/public/plantillas/8. ESTUDIO DEL MERCADO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\essin\OneDrive - Universidad Autónoma del Estado de México\Documents\FORMATOS\PLANTILLAS\AD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\expedientesGrandes.temascalcingo.gob.mx\public\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B56A5F7F-4D86-4872-A13E-3EC9F183EA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86ABE408-EB63-469D-8224-A19778A2AAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{7B13A69E-FB4D-4F6F-8F94-06A932BC66AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{7B13A69E-FB4D-4F6F-8F94-06A932BC66AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="91">
   <si>
     <t xml:space="preserve">ÁREA USUARIA / SOLICITANTE: </t>
   </si>
@@ -282,7 +285,43 @@
     <t>PARTIDA 5 Y 6</t>
   </si>
   <si>
-    <t>MOTONIVELADORA</t>
+    <t>${area}</t>
+  </si>
+  <si>
+    <t>${created_at}</t>
+  </si>
+  <si>
+    <t>${nombre_estudio}</t>
+  </si>
+  <si>
+    <t>${proveedor}</t>
+  </si>
+  <si>
+    <t>${partida}</t>
+  </si>
+  <si>
+    <t>${producto_servicio}</t>
+  </si>
+  <si>
+    <t>${unidad_medida}</t>
+  </si>
+  <si>
+    <t>${cantidad}</t>
+  </si>
+  <si>
+    <t>${precio_unitario}</t>
+  </si>
+  <si>
+    <t>${precio_total}</t>
+  </si>
+  <si>
+    <t>${subtotal}</t>
+  </si>
+  <si>
+    <t>${iva}</t>
+  </si>
+  <si>
+    <t>${total}</t>
   </si>
 </sst>
 </file>
@@ -403,7 +442,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -844,25 +883,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1087,51 +1113,6 @@
     <xf numFmtId="4" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1147,6 +1128,177 @@
     <xf numFmtId="14" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1165,201 +1317,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="44" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1376,9 +1348,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1416,7 +1388,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1522,7 +1494,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1664,7 +1636,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1676,74 +1648,73 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T39"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
     <col min="11" max="11" width="36" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
       <c r="L1" s="31"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
       <c r="P1" s="31"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="151"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
+    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
       <c r="L2" s="3"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="151"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -1754,18 +1725,18 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="151"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="85"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1774,7 +1745,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -1793,7 +1764,7 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -1801,18 +1772,18 @@
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
       <c r="H6" s="31"/>
-      <c r="I6" s="125"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="125"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="125"/>
-      <c r="P6" s="125"/>
-      <c r="Q6" s="125"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="87"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1833,7 +1804,7 @@
       <c r="Q7" s="32"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>1</v>
       </c>
@@ -1847,7 +1818,7 @@
       <c r="H8" s="32"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:20" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -1859,7 +1830,7 @@
       <c r="O9" s="20"/>
       <c r="R9" s="7"/>
     </row>
-    <row r="10" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
@@ -1875,127 +1846,127 @@
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="148"/>
-      <c r="P10" s="148"/>
-      <c r="Q10" s="148"/>
-      <c r="R10" s="148"/>
-    </row>
-    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="156" t="s">
+      <c r="O10" s="109"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="109"/>
+      <c r="R10" s="109"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="158" t="s">
+      <c r="C11" s="100"/>
+      <c r="D11" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="158" t="s">
+      <c r="E11" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="141" t="s">
+      <c r="F11" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="142"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="141" t="s">
+      <c r="G11" s="105"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="142"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="141" t="s">
+      <c r="J11" s="105"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="M11" s="142"/>
-      <c r="N11" s="143"/>
-      <c r="O11" s="141" t="s">
+      <c r="M11" s="105"/>
+      <c r="N11" s="106"/>
+      <c r="O11" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="142"/>
-      <c r="Q11" s="143"/>
-      <c r="R11" s="149" t="s">
+      <c r="P11" s="105"/>
+      <c r="Q11" s="106"/>
+      <c r="R11" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="150"/>
-      <c r="T11" s="150"/>
-    </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="115" t="s">
+      <c r="S11" s="111"/>
+      <c r="T11" s="111"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="144" t="s">
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="145"/>
-      <c r="H12" s="146" t="s">
+      <c r="G12" s="93"/>
+      <c r="H12" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="144" t="s">
+      <c r="I12" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="145"/>
-      <c r="K12" s="146" t="s">
+      <c r="J12" s="93"/>
+      <c r="K12" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="144" t="s">
+      <c r="L12" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="145"/>
-      <c r="N12" s="146" t="s">
+      <c r="M12" s="93"/>
+      <c r="N12" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="144" t="s">
+      <c r="O12" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="145"/>
-      <c r="Q12" s="146" t="s">
+      <c r="P12" s="93"/>
+      <c r="Q12" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="R12" s="149"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-    </row>
-    <row r="13" spans="1:20" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="154"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="159"/>
-      <c r="E13" s="159"/>
+      <c r="R12" s="110"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+    </row>
+    <row r="13" spans="1:20" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="96"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
       <c r="F13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="153"/>
+      <c r="H13" s="94"/>
       <c r="I13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="147"/>
+      <c r="K13" s="91"/>
       <c r="L13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N13" s="147"/>
+      <c r="N13" s="91"/>
       <c r="O13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="149"/>
-      <c r="S13" s="150"/>
-      <c r="T13" s="150"/>
-    </row>
-    <row r="14" spans="1:20" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q13" s="91"/>
+      <c r="R13" s="110"/>
+      <c r="S13" s="111"/>
+      <c r="T13" s="111"/>
+    </row>
+    <row r="14" spans="1:20" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="24">
         <v>1</v>
       </c>
@@ -2044,14 +2015,14 @@
       <c r="Q14" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="139">
+      <c r="R14" s="107">
         <f>(G33+J33+M33+P33)/4</f>
         <v>26314945.015899997</v>
       </c>
-      <c r="S14" s="140"/>
-      <c r="T14" s="140"/>
-    </row>
-    <row r="15" spans="1:20" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+    </row>
+    <row r="15" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
         <v>2</v>
       </c>
@@ -2100,11 +2071,11 @@
       <c r="Q15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="139"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="140"/>
-    </row>
-    <row r="16" spans="1:20" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="107"/>
+      <c r="S15" s="108"/>
+      <c r="T15" s="108"/>
+    </row>
+    <row r="16" spans="1:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35">
         <v>3</v>
       </c>
@@ -2155,11 +2126,11 @@
       <c r="Q16" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R16" s="139"/>
-      <c r="S16" s="140"/>
-      <c r="T16" s="140"/>
-    </row>
-    <row r="17" spans="2:20" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R16" s="107"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+    </row>
+    <row r="17" spans="2:20" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="10">
         <v>4</v>
       </c>
@@ -2203,11 +2174,11 @@
       <c r="Q17" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R17" s="139"/>
-      <c r="S17" s="140"/>
-      <c r="T17" s="140"/>
-    </row>
-    <row r="18" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="107"/>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+    </row>
+    <row r="18" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="35">
         <v>5</v>
       </c>
@@ -2246,11 +2217,11 @@
         <v>0</v>
       </c>
       <c r="Q18" s="29"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="140"/>
-      <c r="T18" s="140"/>
-    </row>
-    <row r="19" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R18" s="107"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+    </row>
+    <row r="19" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>6</v>
       </c>
@@ -2289,11 +2260,11 @@
         <v>0</v>
       </c>
       <c r="Q19" s="29"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="140"/>
-      <c r="T19" s="140"/>
-    </row>
-    <row r="20" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R19" s="107"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+    </row>
+    <row r="20" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="35">
         <v>7</v>
       </c>
@@ -2340,11 +2311,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="29"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="140"/>
-      <c r="T20" s="140"/>
-    </row>
-    <row r="21" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R20" s="107"/>
+      <c r="S20" s="108"/>
+      <c r="T20" s="108"/>
+    </row>
+    <row r="21" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10">
         <v>8</v>
       </c>
@@ -2387,11 +2358,11 @@
         <v>0</v>
       </c>
       <c r="Q21" s="29"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="140"/>
-      <c r="T21" s="140"/>
-    </row>
-    <row r="22" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="107"/>
+      <c r="S21" s="108"/>
+      <c r="T21" s="108"/>
+    </row>
+    <row r="22" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="35">
         <v>9</v>
       </c>
@@ -2430,11 +2401,11 @@
         <v>0</v>
       </c>
       <c r="Q22" s="29"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="140"/>
-      <c r="T22" s="140"/>
-    </row>
-    <row r="23" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R22" s="107"/>
+      <c r="S22" s="108"/>
+      <c r="T22" s="108"/>
+    </row>
+    <row r="23" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="10">
         <v>10</v>
       </c>
@@ -2479,11 +2450,11 @@
         <v>0</v>
       </c>
       <c r="Q23" s="29"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="140"/>
-      <c r="T23" s="140"/>
-    </row>
-    <row r="24" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R23" s="107"/>
+      <c r="S23" s="108"/>
+      <c r="T23" s="108"/>
+    </row>
+    <row r="24" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="35">
         <v>11</v>
       </c>
@@ -2522,11 +2493,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="29"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="140"/>
-      <c r="T24" s="140"/>
-    </row>
-    <row r="25" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R24" s="107"/>
+      <c r="S24" s="108"/>
+      <c r="T24" s="108"/>
+    </row>
+    <row r="25" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="10">
         <v>12</v>
       </c>
@@ -2565,11 +2536,11 @@
         <v>0</v>
       </c>
       <c r="Q25" s="29"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="140"/>
-    </row>
-    <row r="26" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R25" s="107"/>
+      <c r="S25" s="108"/>
+      <c r="T25" s="108"/>
+    </row>
+    <row r="26" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="35">
         <v>13</v>
       </c>
@@ -2608,11 +2579,11 @@
         <v>0</v>
       </c>
       <c r="Q26" s="29"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="140"/>
-      <c r="T26" s="140"/>
-    </row>
-    <row r="27" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R26" s="107"/>
+      <c r="S26" s="108"/>
+      <c r="T26" s="108"/>
+    </row>
+    <row r="27" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="10">
         <v>14</v>
       </c>
@@ -2651,11 +2622,11 @@
         <v>0</v>
       </c>
       <c r="Q27" s="29"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="140"/>
-      <c r="T27" s="140"/>
-    </row>
-    <row r="28" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R27" s="107"/>
+      <c r="S27" s="108"/>
+      <c r="T27" s="108"/>
+    </row>
+    <row r="28" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="35">
         <v>15</v>
       </c>
@@ -2694,11 +2665,11 @@
         <v>0</v>
       </c>
       <c r="Q28" s="29"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="140"/>
-      <c r="T28" s="140"/>
-    </row>
-    <row r="29" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R28" s="107"/>
+      <c r="S28" s="108"/>
+      <c r="T28" s="108"/>
+    </row>
+    <row r="29" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>16</v>
       </c>
@@ -2740,7 +2711,7 @@
       <c r="S29" s="38"/>
       <c r="T29" s="38"/>
     </row>
-    <row r="30" spans="2:20" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>17</v>
       </c>
@@ -2782,7 +2753,7 @@
       <c r="S30" s="38"/>
       <c r="T30" s="38"/>
     </row>
-    <row r="31" spans="2:20" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
       <c r="D31" s="26"/>
@@ -2823,7 +2794,7 @@
       <c r="Q31" s="16"/>
       <c r="R31" s="21"/>
     </row>
-    <row r="32" spans="2:20" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B32" s="12"/>
       <c r="C32" s="13"/>
       <c r="D32" s="12"/>
@@ -2862,7 +2833,7 @@
       <c r="Q32" s="16"/>
       <c r="R32" s="21"/>
     </row>
-    <row r="33" spans="2:17" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -2900,33 +2871,44 @@
       </c>
       <c r="Q33" s="16"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C36" s="33" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="108" t="s">
+      <c r="G36" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="108"/>
-      <c r="I36" s="108"/>
-      <c r="J36" s="108"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C39" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="152" t="s">
+      <c r="G39" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="H39" s="152"/>
-      <c r="I39" s="152"/>
-      <c r="J39" s="152"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="R14:T28"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="R11:T13"/>
     <mergeCell ref="A1:K4"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="G36:J36"/>
@@ -2942,17 +2924,6 @@
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I11:K11"/>
-    <mergeCell ref="R14:T28"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:Q13"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="R11:T13"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.3385826771653544" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="27" orientation="landscape" r:id="rId1"/>
@@ -2969,40 +2940,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="21.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" customWidth="1"/>
-    <col min="11" max="11" width="19.88671875" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="22.21875" customWidth="1"/>
-    <col min="15" max="15" width="21.5546875" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" customWidth="1"/>
-    <col min="19" max="19" width="18.5546875" style="33" customWidth="1"/>
-    <col min="20" max="20" width="17.109375" customWidth="1"/>
-    <col min="21" max="21" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" style="33" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="124"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
+    <row r="1" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="86"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
       <c r="J1" s="46"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -3011,30 +2981,30 @@
       <c r="O1" s="31"/>
       <c r="P1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="124"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+    <row r="2" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
       <c r="J2" s="46"/>
       <c r="K2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="124"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
+    <row r="3" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
       <c r="J3" s="46"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -3046,16 +3016,16 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="124"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="124"/>
+    <row r="4" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="46"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -3065,7 +3035,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="31"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -3073,41 +3043,41 @@
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
       <c r="J5" s="47"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
       <c r="M5" s="47"/>
-      <c r="N5" s="125"/>
-      <c r="O5" s="125"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
       <c r="P5" s="47"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="167"/>
-      <c r="K6" s="167"/>
-      <c r="L6" s="167"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
       <c r="O6" s="32"/>
       <c r="P6" s="32"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>1</v>
       </c>
@@ -3121,7 +3091,7 @@
       <c r="G7" s="32"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -3132,159 +3102,159 @@
       <c r="N8" s="20"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:21" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="136" t="s">
+    <row r="9" spans="1:21" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="137"/>
-      <c r="C9" s="137" t="s">
+      <c r="B9" s="115"/>
+      <c r="C9" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="137"/>
-      <c r="P9" s="138"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="116"/>
       <c r="Q9" s="53"/>
     </row>
-    <row r="10" spans="1:21" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="114" t="s">
+    <row r="10" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="109" t="s">
+      <c r="B10" s="119"/>
+      <c r="C10" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="119" t="s">
+      <c r="E10" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="109" t="s">
+      <c r="F10" s="140"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109" t="s">
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109" t="s">
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="109"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="128" t="s">
+      <c r="O10" s="112"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="129"/>
-      <c r="S10" s="111" t="s">
+      <c r="R10" s="134"/>
+      <c r="S10" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="T10" s="112"/>
-      <c r="U10" s="113"/>
-    </row>
-    <row r="11" spans="1:21" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="114" t="s">
+      <c r="T10" s="131"/>
+      <c r="U10" s="132"/>
+    </row>
+    <row r="11" spans="1:21" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="116" t="s">
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="110" t="s">
+      <c r="F11" s="119"/>
+      <c r="G11" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="116" t="s">
+      <c r="H11" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="116"/>
-      <c r="J11" s="109" t="s">
+      <c r="I11" s="119"/>
+      <c r="J11" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="116" t="s">
+      <c r="K11" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="116"/>
-      <c r="M11" s="109" t="s">
+      <c r="L11" s="119"/>
+      <c r="M11" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="116" t="s">
+      <c r="N11" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="O11" s="116"/>
-      <c r="P11" s="122" t="s">
+      <c r="O11" s="119"/>
+      <c r="P11" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="131"/>
-      <c r="S11" s="100" t="s">
+      <c r="Q11" s="135"/>
+      <c r="R11" s="136"/>
+      <c r="S11" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="T11" s="100" t="s">
+      <c r="T11" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="U11" s="102" t="s">
+      <c r="U11" s="144" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="168"/>
-      <c r="B12" s="169"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
+    <row r="12" spans="1:21" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="122"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="120"/>
       <c r="E12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="159"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="163"/>
+      <c r="J12" s="120"/>
       <c r="K12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="163"/>
+      <c r="M12" s="120"/>
       <c r="N12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="P12" s="162"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="133"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="101"/>
-      <c r="U12" s="103"/>
-    </row>
-    <row r="13" spans="1:21" ht="84" x14ac:dyDescent="0.3">
+      <c r="P12" s="127"/>
+      <c r="Q12" s="137"/>
+      <c r="R12" s="138"/>
+      <c r="S12" s="143"/>
+      <c r="T12" s="143"/>
+      <c r="U12" s="145"/>
+    </row>
+    <row r="13" spans="1:21" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A13" s="59">
         <v>1</v>
       </c>
@@ -3328,11 +3298,11 @@
         <v>0</v>
       </c>
       <c r="P13" s="61"/>
-      <c r="Q13" s="164">
+      <c r="Q13" s="128">
         <f>((F13+I13+L13)/3)*1.16</f>
         <v>5264330.9698666651</v>
       </c>
-      <c r="R13" s="165"/>
+      <c r="R13" s="129"/>
       <c r="S13" s="71">
         <f>+Q13+Q14</f>
         <v>7771875.9529330656</v>
@@ -3346,7 +3316,7 @@
         <v>2054583.6132000003</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A14" s="62">
         <v>2</v>
       </c>
@@ -3389,13 +3359,13 @@
         <v>0</v>
       </c>
       <c r="P14" s="63"/>
-      <c r="Q14" s="160">
+      <c r="Q14" s="125">
         <f>((F14+I14+L14)/3)*1.16</f>
         <v>2507544.9830664</v>
       </c>
-      <c r="R14" s="161"/>
-    </row>
-    <row r="15" spans="1:21" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="R14" s="126"/>
+    </row>
+    <row r="15" spans="1:21" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="62">
         <v>3</v>
       </c>
@@ -3441,14 +3411,14 @@
         <v>3264000</v>
       </c>
       <c r="P15" s="63"/>
-      <c r="Q15" s="160">
+      <c r="Q15" s="125">
         <f>((F15+I15+O15)/3)*1.16</f>
         <v>4308026.8345333328</v>
       </c>
-      <c r="R15" s="161"/>
+      <c r="R15" s="126"/>
       <c r="S15" s="48"/>
     </row>
-    <row r="16" spans="1:21" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="62">
         <v>4</v>
       </c>
@@ -3494,13 +3464,13 @@
         <v>2102400</v>
       </c>
       <c r="P16" s="63"/>
-      <c r="Q16" s="160">
+      <c r="Q16" s="125">
         <f>((F16+I16+O16)/3)*1.16</f>
         <v>2913686.3102666666</v>
       </c>
-      <c r="R16" s="161"/>
-    </row>
-    <row r="17" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="R16" s="126"/>
+    </row>
+    <row r="17" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="62">
         <v>5</v>
       </c>
@@ -3540,13 +3510,13 @@
         <v>4032000</v>
       </c>
       <c r="P17" s="63"/>
-      <c r="Q17" s="160">
+      <c r="Q17" s="125">
         <f>((F17+I17+O17)/3)*1.16</f>
         <v>5305830.480266666</v>
       </c>
-      <c r="R17" s="161"/>
-    </row>
-    <row r="18" spans="1:18" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="126"/>
+    </row>
+    <row r="18" spans="1:18" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="64">
         <v>6</v>
       </c>
@@ -3589,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="P18" s="70"/>
-      <c r="Q18" s="160">
+      <c r="Q18" s="125">
         <f>(F18+L18+I18)/3*1.16</f>
         <v>2054583.6132000003</v>
       </c>
-      <c r="R18" s="161"/>
-    </row>
-    <row r="19" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="R18" s="126"/>
+    </row>
+    <row r="19" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="45"/>
@@ -3634,7 +3604,7 @@
       <c r="P19" s="16"/>
       <c r="Q19" s="21"/>
     </row>
-    <row r="20" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="13"/>
       <c r="C20" s="12"/>
@@ -3673,7 +3643,7 @@
       <c r="P20" s="16"/>
       <c r="Q20" s="21"/>
     </row>
-    <row r="21" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -3711,22 +3681,22 @@
       </c>
       <c r="P21" s="16"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E25" s="108" t="s">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E25" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="108"/>
-      <c r="O25" s="108" t="s">
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="O25" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="P25" s="108"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="108"/>
-    </row>
-    <row r="27" spans="1:18" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+    </row>
+    <row r="27" spans="1:18" ht="117" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E29" s="55"/>
       <c r="F29" s="55"/>
       <c r="G29" s="55"/>
@@ -3736,32 +3706,55 @@
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E30" s="104" t="s">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E30" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="O30" s="104" t="s">
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="147"/>
+      <c r="O30" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="105"/>
-      <c r="R30" s="105"/>
-    </row>
-    <row r="31" spans="1:18" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
-      <c r="R31" s="105"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="147"/>
+      <c r="R30" s="147"/>
+    </row>
+    <row r="31" spans="1:18" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="147"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="147"/>
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="147"/>
+      <c r="R31" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E30:H31"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="O30:R31"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="Q10:R12"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
     <mergeCell ref="A1:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="K5:L5"/>
@@ -3778,29 +3771,6 @@
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="Q10:R12"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E30:H31"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="O30:R31"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.3385826771653544" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="34" orientation="landscape" r:id="rId1"/>
@@ -3816,41 +3786,41 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="21.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" customWidth="1"/>
-    <col min="11" max="11" width="19.88671875" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="22.21875" customWidth="1"/>
-    <col min="15" max="15" width="21.5546875" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" customWidth="1"/>
-    <col min="19" max="19" width="18.5546875" style="33" customWidth="1"/>
-    <col min="20" max="20" width="17.109375" customWidth="1"/>
-    <col min="21" max="21" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" style="33" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="124"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="86"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
       <c r="J1" s="46"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -3859,30 +3829,30 @@
       <c r="O1" s="31"/>
       <c r="P1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="124"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+    <row r="2" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
       <c r="J2" s="46"/>
       <c r="K2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="124"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
+    <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
       <c r="J3" s="46"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -3894,16 +3864,16 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="124"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="124"/>
+    <row r="4" spans="1:19" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="46"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -3913,7 +3883,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="31"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -3921,46 +3891,46 @@
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
       <c r="J5" s="47"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
       <c r="M5" s="47"/>
-      <c r="N5" s="125"/>
-      <c r="O5" s="125"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
       <c r="P5" s="47"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="134" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
+      <c r="C6" s="149" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="150"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="150"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
       <c r="O6" s="32"/>
       <c r="P6" s="32"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="99">
-        <v>45945</v>
+      <c r="B7" s="84" t="s">
+        <v>79</v>
       </c>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
@@ -3969,7 +3939,7 @@
       <c r="G7" s="32"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -3980,668 +3950,297 @@
       <c r="N8" s="20"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:21" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="136" t="s">
+    <row r="9" spans="1:19" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="137"/>
-      <c r="C9" s="137" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="137"/>
-      <c r="P9" s="138"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="115" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="116"/>
       <c r="Q9" s="53"/>
     </row>
-    <row r="10" spans="1:21" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="114" t="s">
+    <row r="10" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="109" t="s">
+      <c r="B10" s="119"/>
+      <c r="C10" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="119" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109" t="s">
-        <v>59</v>
-      </c>
-      <c r="O10" s="109"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="128" t="s">
+      <c r="E10" s="139" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="140"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="133" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="129"/>
-      <c r="S10" s="111" t="s">
+      <c r="I10" s="134"/>
+      <c r="J10" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="T10" s="112"/>
-      <c r="U10" s="113"/>
-    </row>
-    <row r="11" spans="1:21" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="114" t="s">
+      <c r="K10" s="131"/>
+      <c r="L10" s="132"/>
+      <c r="S10"/>
+    </row>
+    <row r="11" spans="1:19" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="116" t="s">
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="110" t="s">
+      <c r="F11" s="119"/>
+      <c r="G11" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="116" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="116"/>
-      <c r="J11" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="116" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="116"/>
-      <c r="M11" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" s="116" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="116"/>
-      <c r="P11" s="122" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="131"/>
-      <c r="S11" s="100" t="s">
+      <c r="H11" s="135"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="T11" s="100" t="s">
+      <c r="K11" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="102" t="s">
+      <c r="L11" s="144" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="115"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
+      <c r="S11"/>
+    </row>
+    <row r="12" spans="1:19" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="95"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
       <c r="E12" s="73" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="118"/>
-      <c r="H12" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="73" t="s">
+      <c r="G12" s="102"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="145"/>
+      <c r="S12"/>
+    </row>
+    <row r="13" spans="1:19" ht="33" x14ac:dyDescent="0.25">
+      <c r="A13" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="79"/>
+      <c r="H13" s="151" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="148"/>
+      <c r="J13" s="80" t="e">
+        <f>+H13+#REF!+#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K13" s="81" t="e">
+        <f>+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L13" s="81" t="e">
+        <f>+#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S13"/>
+    </row>
+    <row r="14" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="21"/>
+      <c r="J14" s="33"/>
+      <c r="S14"/>
+    </row>
+    <row r="15" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="21"/>
+      <c r="J15" s="48"/>
+      <c r="S15"/>
+    </row>
+    <row r="16" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="110"/>
-      <c r="K12" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="73" t="s">
+      <c r="F16" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="110"/>
-      <c r="N12" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="O12" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="133"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="101"/>
-      <c r="U12" s="103"/>
-    </row>
-    <row r="13" spans="1:21" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="74">
-        <v>1</v>
-      </c>
-      <c r="B13" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="77">
-        <v>1</v>
-      </c>
-      <c r="E13" s="78">
-        <v>4341238.71</v>
-      </c>
-      <c r="F13" s="78">
-        <f t="shared" ref="F13:F16" si="0">E13*D13</f>
-        <v>4341238.71</v>
-      </c>
-      <c r="G13" s="79"/>
-      <c r="H13" s="78">
-        <v>3536210</v>
-      </c>
-      <c r="I13" s="78">
-        <f t="shared" ref="I13:I18" si="1">H13*D13</f>
-        <v>3536210</v>
-      </c>
-      <c r="J13" s="79"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78">
-        <f>K13*D13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="79"/>
-      <c r="N13" s="78">
-        <v>3264000</v>
-      </c>
-      <c r="O13" s="78">
-        <f>N13*D13</f>
-        <v>3264000</v>
-      </c>
-      <c r="P13" s="80"/>
-      <c r="Q13" s="126">
-        <f>((F13+I13+O13)/3)*1.16</f>
-        <v>4308026.8345333328</v>
-      </c>
-      <c r="R13" s="127"/>
-      <c r="S13" s="95">
-        <f>+Q13+Q14+Q15</f>
-        <v>12527543.625066666</v>
-      </c>
-      <c r="T13" s="96">
-        <f>+Q16</f>
-        <v>2054583.6132000003</v>
-      </c>
-      <c r="U13" s="96">
-        <f>+Q17+Q18</f>
-        <v>7771875.9529330647</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="81">
-        <v>2</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="84">
-        <v>1</v>
-      </c>
-      <c r="E14" s="85">
-        <v>2945568.63</v>
-      </c>
-      <c r="F14" s="85">
-        <f t="shared" si="0"/>
-        <v>2945568.63</v>
-      </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="85">
-        <v>2487427</v>
-      </c>
-      <c r="I14" s="85">
-        <f t="shared" si="1"/>
-        <v>2487427</v>
-      </c>
-      <c r="J14" s="86"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="85">
-        <f>K14*D14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="86"/>
-      <c r="N14" s="85">
-        <v>2102400</v>
-      </c>
-      <c r="O14" s="85">
-        <f>N14*D14</f>
-        <v>2102400</v>
-      </c>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="106">
-        <f>((F14+I14+O14)/3)*1.16</f>
-        <v>2913686.3102666666</v>
-      </c>
-      <c r="R14" s="107"/>
-    </row>
-    <row r="15" spans="1:21" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="81">
-        <v>3</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="84">
-        <v>1</v>
-      </c>
-      <c r="E15" s="85">
-        <v>5363623.38</v>
-      </c>
-      <c r="F15" s="85">
-        <f t="shared" si="0"/>
-        <v>5363623.38</v>
-      </c>
-      <c r="G15" s="86"/>
-      <c r="H15" s="85">
-        <v>4326352</v>
-      </c>
-      <c r="I15" s="85">
-        <f t="shared" si="1"/>
-        <v>4326352</v>
-      </c>
-      <c r="J15" s="86"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="85">
-        <v>4032000</v>
-      </c>
-      <c r="O15" s="85">
-        <f>N15*D15</f>
-        <v>4032000</v>
-      </c>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="106">
-        <f>((F15+I15+O15)/3)*1.16</f>
-        <v>5305830.480266666</v>
-      </c>
-      <c r="R15" s="107"/>
-      <c r="S15" s="48"/>
-    </row>
-    <row r="16" spans="1:21" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="81">
-        <v>4</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="84">
-        <v>3</v>
-      </c>
-      <c r="E16" s="85">
-        <v>590000</v>
-      </c>
-      <c r="F16" s="85">
-        <f t="shared" si="0"/>
-        <v>1770000</v>
-      </c>
-      <c r="G16" s="86"/>
-      <c r="H16" s="85">
-        <v>589568.97</v>
-      </c>
-      <c r="I16" s="85">
-        <f t="shared" si="1"/>
-        <v>1768706.91</v>
-      </c>
-      <c r="J16" s="86"/>
-      <c r="K16" s="85">
-        <v>591623.80000000005</v>
-      </c>
-      <c r="L16" s="85">
-        <f>K16*D16</f>
-        <v>1774871.4000000001</v>
-      </c>
-      <c r="M16" s="86"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85">
-        <f>N16*D16</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="106">
-        <f>((F16+I16+L16)/3)*1.16</f>
-        <v>2054583.6132000003</v>
-      </c>
-      <c r="R16" s="107"/>
-    </row>
-    <row r="17" spans="1:18" ht="84" x14ac:dyDescent="0.3">
-      <c r="A17" s="81">
-        <v>5</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="84">
-        <v>2</v>
-      </c>
-      <c r="E17" s="85">
-        <v>2268775</v>
-      </c>
-      <c r="F17" s="85">
-        <f>E17*D17</f>
-        <v>4537550</v>
-      </c>
-      <c r="G17" s="83"/>
-      <c r="H17" s="85">
-        <v>2094827.59</v>
-      </c>
-      <c r="I17" s="85">
-        <f t="shared" si="1"/>
-        <v>4189655.18</v>
-      </c>
-      <c r="J17" s="86"/>
-      <c r="K17" s="85">
-        <v>2443721.94</v>
-      </c>
-      <c r="L17" s="85">
-        <f>K17*D17</f>
-        <v>4887443.88</v>
-      </c>
-      <c r="M17" s="86"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85">
-        <f>+N17*D17</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="106">
-        <f>((F17+I17+L17)/3)*1.16</f>
-        <v>5264330.9698666651</v>
-      </c>
-      <c r="R17" s="107"/>
-    </row>
-    <row r="18" spans="1:18" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="88">
-        <v>6</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="91">
-        <v>1</v>
-      </c>
-      <c r="E18" s="92">
-        <v>2234482.75862</v>
-      </c>
-      <c r="F18" s="92">
-        <f>D18*E18</f>
-        <v>2234482.75862</v>
-      </c>
-      <c r="G18" s="93"/>
-      <c r="H18" s="92">
-        <v>2092593.97</v>
-      </c>
-      <c r="I18" s="92">
-        <f t="shared" si="1"/>
-        <v>2092593.97</v>
-      </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="92">
-        <v>2157953.4</v>
-      </c>
-      <c r="L18" s="92">
-        <f>K18*D18</f>
-        <v>2157953.4</v>
-      </c>
-      <c r="M18" s="93"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="92">
-        <f>+N18*D18</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="106">
-        <f>(F18+L18+I18)/3*1.16</f>
-        <v>2507544.9830663996</v>
-      </c>
-      <c r="R18" s="107"/>
-    </row>
-    <row r="19" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="97">
-        <f>SUM(F13:F18)</f>
-        <v>21192463.47862</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="97">
-        <f>SUM(I13:I18)</f>
-        <v>18400945.059999999</v>
-      </c>
-      <c r="J19" s="52"/>
-      <c r="K19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="97">
-        <f>SUM(L13:L18)</f>
-        <v>8820268.6799999997</v>
-      </c>
-      <c r="M19" s="16"/>
-      <c r="N19" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="O19" s="97">
-        <f>SUM(O13:O18)</f>
-        <v>9398400</v>
-      </c>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="21"/>
-    </row>
-    <row r="20" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="98">
-        <f>F19*0.16</f>
-        <v>3390794.1565792002</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="98">
-        <f>I19*16%</f>
-        <v>2944151.2095999997</v>
-      </c>
-      <c r="J20" s="52"/>
-      <c r="K20" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L20" s="98">
-        <f>L19*16%</f>
-        <v>1411242.9887999999</v>
-      </c>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="O20" s="98">
-        <f>O19*16%</f>
-        <v>1503744</v>
-      </c>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="21"/>
-    </row>
-    <row r="21" spans="1:18" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="98">
-        <f>SUM(F19:F20)</f>
-        <v>24583257.6351992</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="98">
-        <f>SUM(I19:I20)</f>
-        <v>21345096.269599997</v>
-      </c>
+      <c r="I16" s="83" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J16" s="33"/>
+      <c r="S16"/>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="J17" s="33"/>
+      <c r="S17"/>
+    </row>
+    <row r="18" spans="5:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="33"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="J19" s="33"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E20" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="J20" s="33"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="5:19" ht="16.5" x14ac:dyDescent="0.25">
       <c r="J21" s="16"/>
-      <c r="K21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L21" s="98">
-        <f>SUM(L19:L20)</f>
-        <v>10231511.6688</v>
-      </c>
-      <c r="M21" s="16"/>
-      <c r="N21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O21" s="98">
-        <f>SUM(O19:O20)</f>
-        <v>10902144</v>
-      </c>
-      <c r="P21" s="16"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E25" s="108" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="108"/>
-      <c r="O25" s="108" t="s">
+      <c r="M21" s="33"/>
+      <c r="S21"/>
+    </row>
+    <row r="24" spans="5:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E25" s="146" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="147"/>
+      <c r="O25" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="P25" s="108"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="108"/>
-    </row>
-    <row r="27" spans="1:18" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="147"/>
+    </row>
+    <row r="27" spans="5:19" ht="117" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="5:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O29" s="55"/>
       <c r="P29" s="55"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E30" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="O30" s="104" t="s">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="O30" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="105"/>
-      <c r="R30" s="105"/>
-    </row>
-    <row r="31" spans="1:18" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
-      <c r="R31" s="105"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="147"/>
+      <c r="R30" s="147"/>
+    </row>
+    <row r="31" spans="5:19" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="147"/>
+      <c r="R31" s="147"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="25">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="E25:H26"/>
+    <mergeCell ref="O30:R31"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="A1:I4"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="Q10:R12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H10:I12"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="C6:L6"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:P9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="E30:H31"/>
-    <mergeCell ref="O30:R31"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.3385826771653544" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="34" orientation="landscape" r:id="rId1"/>
